--- a/Encoding_A.xlsx
+++ b/Encoding_A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Fernanda/Library/CloudStorage/Box-Box/Leal Lab/Shared Resources/New Emotional Image Sets/A+B NEW/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mc151/Library/CloudStorage/Box-Box/Leal Lab/Shared Resources/New Emotional Image Sets/Emotional MDT_A+B Sets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203FD656-C6D0-6047-BDBB-6F826A96CE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB82572-33FE-DF49-B219-D5A6A4B26E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8560" yWindow="1220" windowWidth="28800" windowHeight="16520" xr2:uid="{0A5B453C-D9CB-5846-AFE3-8AE1058DC74D}"/>
+    <workbookView xWindow="2520" yWindow="2340" windowWidth="29820" windowHeight="16520" xr2:uid="{0A5B453C-D9CB-5846-AFE3-8AE1058DC74D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,9 +127,6 @@
     <t>2043_A_H.jpg</t>
   </si>
   <si>
-    <t>601X.jpg</t>
-  </si>
-  <si>
     <t>1060_A_L.jpg</t>
   </si>
   <si>
@@ -151,15 +148,9 @@
     <t>3039_A_H.jpg</t>
   </si>
   <si>
-    <t>320D.jpg</t>
-  </si>
-  <si>
     <t>2045_A_L.jpg</t>
   </si>
   <si>
-    <t>351A.jpg</t>
-  </si>
-  <si>
     <t>2069_C_X.jpg</t>
   </si>
   <si>
@@ -169,9 +160,6 @@
     <t>1057_A_H.jpg</t>
   </si>
   <si>
-    <t>366A.jpg</t>
-  </si>
-  <si>
     <t>3074_C_X.jpg</t>
   </si>
   <si>
@@ -220,9 +208,6 @@
     <t>2062_C_X.jpg</t>
   </si>
   <si>
-    <t>306E.jpg</t>
-  </si>
-  <si>
     <t>3021_A_L.jpg</t>
   </si>
   <si>
@@ -262,9 +247,6 @@
     <t>2014_A_H.jpg</t>
   </si>
   <si>
-    <t>354A.jpg</t>
-  </si>
-  <si>
     <t>2040_A_H.jpg</t>
   </si>
   <si>
@@ -376,9 +358,6 @@
     <t>2076_C_X.jpg</t>
   </si>
   <si>
-    <t>1054_A_L.jpg</t>
-  </si>
-  <si>
     <t>1033_A_H.jpg</t>
   </si>
   <si>
@@ -403,7 +382,28 @@
     <t>1062_C_X.jpg</t>
   </si>
   <si>
-    <t>359A.jpg</t>
+    <t>1015_A_H.jpg</t>
+  </si>
+  <si>
+    <t>1047_A_L.jpg</t>
+  </si>
+  <si>
+    <t>1039_B_L.jpg</t>
+  </si>
+  <si>
+    <t>1067_C_X.jpg</t>
+  </si>
+  <si>
+    <t>1044_A_H.jpg</t>
+  </si>
+  <si>
+    <t>1001_A_L.jpg</t>
+  </si>
+  <si>
+    <t>1073_C_X.jpg</t>
+  </si>
+  <si>
+    <t>1054_A_H.jpg</t>
   </si>
 </sst>
 </file>
@@ -446,7 +446,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -460,17 +460,6 @@
       </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="7"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -495,11 +484,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -884,10 +873,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -897,123 +886,123 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
+      <c r="A3" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>35</v>
+      <c r="A4" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>18</v>
-      </c>
       <c r="B9" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>0</v>
@@ -1023,11 +1012,11 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>13</v>
+      <c r="A12" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
@@ -1038,24 +1027,24 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
@@ -1066,7 +1055,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>5</v>
@@ -1080,7 +1069,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>5</v>
@@ -1094,58 +1083,58 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -1164,21 +1153,21 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>5</v>
@@ -1192,7 +1181,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>4</v>
@@ -1206,24 +1195,24 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>6</v>
@@ -1233,22 +1222,22 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>100</v>
+      <c r="A27" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>5</v>
@@ -1262,21 +1251,21 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>4</v>
@@ -1290,10 +1279,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>6</v>
@@ -1304,10 +1293,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>0</v>
@@ -1317,39 +1306,39 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
-        <v>80</v>
+      <c r="A33" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>0</v>
@@ -1360,52 +1349,52 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>41</v>
+      <c r="A39" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>0</v>
@@ -1416,21 +1405,21 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>3</v>
@@ -1444,24 +1433,24 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>0</v>
@@ -1472,7 +1461,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>5</v>
@@ -1486,10 +1475,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>0</v>
@@ -1500,38 +1489,38 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>6</v>
@@ -1542,24 +1531,24 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
+      <c r="A50" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>6</v>
@@ -1570,10 +1559,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>0</v>
@@ -1584,10 +1573,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>6</v>
@@ -1598,21 +1587,21 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>3</v>
@@ -1626,52 +1615,52 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>6</v>
@@ -1682,24 +1671,24 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>0</v>
@@ -1710,77 +1699,77 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
-        <v>40</v>
+      <c r="A63" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>5</v>
@@ -1789,29 +1778,29 @@
         <v>6</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>0</v>
@@ -1822,108 +1811,108 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
-        <v>43</v>
+      <c r="A76" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>6</v>
@@ -1934,38 +1923,38 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
-        <v>25</v>
+      <c r="A78" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>6</v>
@@ -1976,7 +1965,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>4</v>
@@ -1985,43 +1974,43 @@
         <v>6</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>0</v>
@@ -2031,8 +2020,8 @@
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="7" t="s">
-        <v>63</v>
+      <c r="A84" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>5</v>
@@ -2046,10 +2035,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>6</v>
@@ -2059,106 +2048,106 @@
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="3" t="s">
-        <v>20</v>
+      <c r="A86" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="3" t="s">
-        <v>107</v>
+      <c r="A92" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>4</v>
@@ -2172,24 +2161,24 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>0</v>
@@ -2200,21 +2189,21 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="4" t="s">
-        <v>30</v>
+      <c r="A97" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>3</v>
@@ -2227,53 +2216,53 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="7" t="s">
-        <v>11</v>
+      <c r="A98" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>0</v>
@@ -2284,7 +2273,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>3</v>
@@ -2298,10 +2287,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>6</v>
@@ -2312,7 +2301,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>5</v>
@@ -2326,63 +2315,63 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
-        <v>44</v>
+      <c r="A106" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="7" t="s">
-        <v>98</v>
+      <c r="A109" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>4</v>
@@ -2396,24 +2385,24 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>0</v>
@@ -2423,25 +2412,25 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="3" t="s">
-        <v>116</v>
+      <c r="A112" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="3" t="s">
-        <v>110</v>
+      <c r="A113" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>0</v>
